--- a/rates-nodispo/week-18/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-18/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sev IPM" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BajoRend" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sin Conv" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demanda NC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demanda No Convertida" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Corp" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Destino" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por País" sheetId="8" state="visible" r:id="rId8"/>
@@ -524,7 +524,7 @@
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         <v>28</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.004339739615623063</v>
+        <v>0.004296455424274973</v>
       </c>
     </row>
     <row r="7">
@@ -603,7 +603,7 @@
         <v>226</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.03502789832610043</v>
+        <v>0.03467853306736228</v>
       </c>
     </row>
     <row r="8">
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>950</v>
+        <v>971</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.1472411655300682</v>
+        <v>0.1489949363203928</v>
       </c>
     </row>
     <row r="9">
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.07796032238065716</v>
+        <v>0.07764308731011202</v>
       </c>
     </row>
     <row r="10">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>4745</v>
+        <v>4786</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.7354308741475512</v>
+        <v>0.7343869878778579</v>
       </c>
     </row>
   </sheetData>
@@ -697,7 +697,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>5827</v>
+        <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.9031308121512709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>132</v>
+        <v>6002</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.02045877247365158</v>
+        <v>0.9209759091606567</v>
       </c>
     </row>
     <row r="8">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.02061376317420955</v>
+        <v>0.02056160810188737</v>
       </c>
     </row>
     <row r="9">
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.02278363298202108</v>
+        <v>0.02301672548718735</v>
       </c>
     </row>
     <row r="10">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.03301301921884687</v>
+        <v>0.03544575725026853</v>
       </c>
     </row>
   </sheetData>
@@ -858,7 +858,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7844,7 @@
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7864,7 +7864,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8599,7 @@
         <v>-114.2499999999998</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>0.06641728789635476</v>
+        <v>0.06641728789635475</v>
       </c>
       <c r="G25" s="15" t="n">
         <v>-15.35269129654919</v>
@@ -8739,7 +8739,7 @@
         <v>2278.94</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0.06553750358113819</v>
+        <v>0.0655375035811382</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>451.5186205317004</v>
@@ -8879,7 +8879,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0.03071649846331387</v>
+        <v>0.03071649846331388</v>
       </c>
       <c r="G33" s="15" t="n">
         <v>0</v>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9707,7 +9707,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10687,7 +10687,7 @@
         <v>6065.59</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0.02500874661662356</v>
+        <v>0.02500874661662357</v>
       </c>
       <c r="G32" s="15" t="n">
         <v>422.1475259654633</v>
@@ -11224,7 +11224,7 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
         <v>5002.38</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0.02768542912647766</v>
+        <v>0.02768542912647765</v>
       </c>
       <c r="G51" s="15" t="n">
         <v>596.7443993851685</v>
@@ -11519,7 +11519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11530,7 +11530,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11550,7 +11550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12052,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12647,7 +12647,7 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12717,7 +12717,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12752,7 +12752,7 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12822,7 +12822,7 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12880,7 +12880,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>0.08471755571495086</v>
+        <v>0.08471755571495088</v>
       </c>
       <c r="G42" s="15" t="n">
         <v>0</v>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13347,7 +13347,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13452,7 +13452,7 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13697,7 +13697,7 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13767,7 +13767,7 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13825,7 +13825,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>0.09765795669215852</v>
+        <v>0.0976579566921585</v>
       </c>
       <c r="G69" s="15" t="n">
         <v>0</v>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13872,7 +13872,7 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13907,7 +13907,7 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13977,7 +13977,7 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14047,7 +14047,7 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14117,7 +14117,7 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14222,7 +14222,7 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14257,7 +14257,7 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14362,7 +14362,7 @@
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14397,7 +14397,7 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14432,7 +14432,7 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14677,7 +14677,7 @@
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14922,7 +14922,7 @@
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14992,7 +14992,7 @@
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15027,7 +15027,7 @@
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15272,7 +15272,7 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15307,7 +15307,7 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15412,7 +15412,7 @@
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15447,7 +15447,7 @@
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15517,7 +15517,7 @@
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15587,7 +15587,7 @@
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15657,7 +15657,7 @@
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15727,7 +15727,7 @@
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15832,7 +15832,7 @@
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15867,7 +15867,7 @@
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15902,7 +15902,7 @@
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15937,7 +15937,7 @@
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16007,7 +16007,7 @@
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16112,7 +16112,7 @@
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16287,7 +16287,7 @@
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16497,7 +16497,7 @@
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16602,7 +16602,7 @@
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16672,7 +16672,7 @@
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16707,7 +16707,7 @@
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16847,7 +16847,7 @@
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16882,7 @@
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16917,7 +16917,7 @@
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16952,7 +16952,7 @@
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17057,7 +17057,7 @@
       </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17092,7 +17092,7 @@
       </c>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17197,7 +17197,7 @@
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17232,7 +17232,7 @@
       </c>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17267,7 +17267,7 @@
       </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17337,7 @@
       </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17442,7 +17442,7 @@
       </c>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17452,7 +17452,7 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C173" s="12" t="n">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17487,7 +17487,7 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="C174" s="12" t="n">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,42 @@
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-18/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-18/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -544,7 +544,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
@@ -858,7 +858,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
         <v>0.02955366098691914</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>-6.424450754981815</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>0.04998583953408435</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>-36.23626918924676</v>
+        <v>0</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>0.02653768980512077</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-743.6671641157939</v>
+        <v>0</v>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>0.0133118256822509</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-125.6743177491009</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>0.0416399699855067</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>-293.6829085277479</v>
+        <v>0</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>0.07087493585869134</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>-467.6817705905702</v>
+        <v>0</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>0.3290496372545912</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-104.7652678551024</v>
+        <v>0</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>0.04108139981306019</v>
       </c>
       <c r="J20" s="15" t="n">
-        <v>-104.3720264178027</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>0.09294892906544171</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>-864.7950489860559</v>
+        <v>0</v>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>0.04254958082851609</v>
       </c>
       <c r="J28" s="15" t="n">
-        <v>-879.8111977046948</v>
+        <v>0</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>0.01403716355614342</v>
       </c>
       <c r="J36" s="15" t="n">
-        <v>-139.093099508461</v>
+        <v>0</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>0.002944862558084232</v>
       </c>
       <c r="J50" s="15" t="n">
-        <v>-118.8356802683925</v>
+        <v>0</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>0.05161119428469778</v>
       </c>
       <c r="J51" s="15" t="n">
-        <v>-1422.255347383538</v>
+        <v>0</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>0.06443471374058292</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>-647.7637926181919</v>
+        <v>0</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -5511,7 +5511,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>-104.7652678551024</v>
+        <v>0</v>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>-1814.070816329226</v>
+        <v>0</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>-2014.484614937743</v>
+        <v>0</v>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -7864,7 +7864,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
         <v>0.06641728789635475</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>-15.35269129654919</v>
+        <v>0</v>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>0.01377003600613635</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>-1151.290282680609</v>
+        <v>0</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>0.004224830336804105</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>-41.99281311349937</v>
+        <v>0</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>0.05474299307727622</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>-301.9203439167827</v>
+        <v>0</v>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
@@ -9707,7 +9707,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10130,7 +10130,7 @@
         <v>0.1175984375521412</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-134.0207498668855</v>
+        <v>0</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>0.02932297119156628</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>-75.18990681139714</v>
+        <v>0</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>0.0844021675568204</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>-41.73107731588496</v>
+        <v>0</v>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -11550,7 +11550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
         <v>0.1037674954494018</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>-68.93633420202207</v>
+        <v>0</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>0.04783271122436374</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>-16.81672371014326</v>
+        <v>0</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>0.1646204858673438</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>-242.607220459823</v>
+        <v>0</v>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
